--- a/Experience/users_feeling.xlsx
+++ b/Experience/users_feeling.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fortineau_Vin\Documents\GitHub\Thesis_report\Experience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2114EC-5C68-4A83-A0C3-98C2EDC936CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B992D5CE-6C02-490C-8B2E-B248195DB668}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7650" xr2:uid="{55FBCF9A-0BB1-480D-8040-347006D202D3}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="20">
   <si>
     <t>user</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>0.75</t>
+  </si>
+  <si>
+    <t>"score"</t>
   </si>
 </sst>
 </file>
@@ -438,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE904B40-DF72-4FB2-91F7-1BD448C59B22}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="21.42578125" customWidth="1"/>
@@ -477,17 +480,17 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>8</v>
+      <c r="A2">
+        <v>0</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -495,78 +498,72 @@
       <c r="F2">
         <v>-2</v>
       </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
-      </c>
       <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
+      <c r="F3">
+        <v>-2</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>50</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>-2</v>
+      <c r="F4" t="s">
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="s">
         <v>11</v>
@@ -574,7 +571,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -583,86 +580,86 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
         <v>9</v>
       </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>11</v>
+      <c r="C6">
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
         <v>17</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
       </c>
-      <c r="H7">
-        <v>0</v>
+      <c r="H7" t="s">
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="s">
         <v>11</v>
@@ -670,31 +667,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>-1</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="s">
         <v>11</v>
@@ -702,28 +699,28 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>9</v>
+        <v>-1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -734,7 +731,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>353</v>
+        <v>211</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -752,13 +749,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="s">
         <v>11</v>
@@ -766,7 +763,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -784,21 +781,21 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -812,31 +809,31 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12" t="s">
-        <v>11</v>
+      <c r="F12">
+        <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -844,8 +841,8 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13">
-        <v>-2</v>
+      <c r="F13" t="s">
+        <v>11</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -857,27 +854,27 @@
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14">
-        <v>2</v>
+      <c r="C14" t="s">
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -885,28 +882,28 @@
       <c r="H14" t="s">
         <v>11</v>
       </c>
-      <c r="I14" t="s">
-        <v>11</v>
+      <c r="I14">
+        <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>456</v>
+        <v>418</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" t="s">
-        <v>11</v>
+      <c r="C15">
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -926,31 +923,31 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16">
-        <v>2</v>
+      <c r="C16" t="s">
+        <v>11</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>10</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="H16" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" t="s">
+        <v>11</v>
       </c>
       <c r="J16" t="s">
         <v>11</v>
@@ -958,13 +955,13 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>546</v>
+        <v>495</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -973,16 +970,16 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="s">
         <v>10</v>
       </c>
-      <c r="H17" t="s">
-        <v>17</v>
+      <c r="H17">
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="s">
         <v>11</v>
@@ -990,13 +987,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1005,30 +1002,30 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>-2</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>573</v>
+        <v>548</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1036,11 +1033,11 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" t="s">
-        <v>10</v>
+      <c r="F19">
+        <v>-2</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1049,18 +1046,18 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>640</v>
+        <v>573</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1068,31 +1065,31 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20">
-        <v>0</v>
+      <c r="F20" t="s">
+        <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1101,16 +1098,16 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="s">
         <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="s">
         <v>11</v>
@@ -1118,13 +1115,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1133,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="F22">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G22" t="s">
         <v>9</v>
       </c>
       <c r="H22" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="s">
         <v>11</v>
@@ -1150,13 +1147,13 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>710</v>
+        <v>666</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1165,16 +1162,16 @@
         <v>1</v>
       </c>
       <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23" t="s">
-        <v>11</v>
+        <v>-2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
       </c>
       <c r="J23" t="s">
         <v>11</v>
@@ -1182,60 +1179,63 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>740</v>
+        <v>710</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" t="s">
-        <v>11</v>
-      </c>
-      <c r="I24">
-        <v>2</v>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J24" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>841</v>
+        <v>740</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
-      <c r="C25" t="s">
-        <v>11</v>
+      <c r="C25">
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="s">
         <v>11</v>
@@ -1243,31 +1243,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s">
         <v>10</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="s">
         <v>11</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>922</v>
+        <v>851</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G27" t="s">
         <v>9</v>
       </c>
-      <c r="H27">
-        <v>0</v>
+      <c r="H27" t="s">
+        <v>10</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -1305,8 +1305,37 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>922</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
@@ -1328,6 +1357,9 @@
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experience/users_feeling.xlsx
+++ b/Experience/users_feeling.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20373"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fortineau_Vin\Documents\GitHub\Thesis_report\Experience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fortineau_vin\Documents\GitHub\Thesis_report\Experience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B992D5CE-6C02-490C-8B2E-B248195DB668}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7650" xr2:uid="{55FBCF9A-0BB1-480D-8040-347006D202D3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7650"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="22">
   <si>
     <t>user</t>
   </si>
@@ -85,14 +84,20 @@
   </si>
   <si>
     <t>"score"</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>median</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="000"/>
+    <numFmt numFmtId="164" formatCode="000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -125,7 +130,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -440,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE904B40-DF72-4FB2-91F7-1BD448C59B22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -480,7 +485,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2">
@@ -497,6 +502,12 @@
       </c>
       <c r="F2">
         <v>-2</v>
+      </c>
+      <c r="G2">
+        <v>0.5</v>
+      </c>
+      <c r="H2">
+        <v>1.75</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -1338,10 +1349,46 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30">
+        <f>AVERAGE(B2:B28)</f>
+        <v>0.57692307692307687</v>
+      </c>
+      <c r="C30">
+        <f>AVERAGE(C2:C28)</f>
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="D30">
+        <f>AVERAGE(D2:D28)</f>
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ref="E30:I30" si="0">AVERAGE(E2:E28)</f>
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>-0.58333333333333337</v>
+      </c>
+      <c r="G30">
+        <f>AVERAGE(G2:G28)</f>
+        <v>0.125</v>
+      </c>
+      <c r="H30">
+        <f>AVERAGE(H2:H28)</f>
+        <v>0.21875</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="0"/>
+        <v>0.54166666666666663</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>

--- a/Experience/users_feeling.xlsx
+++ b/Experience/users_feeling.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20373"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fortineau_vin\Documents\GitHub\Thesis_report\Experience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fortineau_Vin\Documents\GitHub\Thesis_report\Experience\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFE81A1-1076-4830-A95F-C3F71CE704E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="26">
   <si>
     <t>user</t>
   </si>
@@ -90,17 +91,37 @@
   </si>
   <si>
     <t>median</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>std dev</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -116,7 +137,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -124,14 +145,150 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,42 +602,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -582,7 +739,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -597,24 +754,24 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -623,86 +780,86 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
         <v>9</v>
       </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
-        <v>11</v>
+      <c r="C7">
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
       </c>
-      <c r="H8">
-        <v>0</v>
+      <c r="H8" t="s">
+        <v>17</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="s">
         <v>11</v>
@@ -710,31 +867,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>-1</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="s">
         <v>11</v>
@@ -742,28 +899,28 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" t="s">
-        <v>9</v>
+        <v>-1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -774,7 +931,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>353</v>
+        <v>211</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -792,13 +949,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="s">
         <v>11</v>
@@ -806,7 +963,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>364</v>
+        <v>278</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -824,21 +981,18 @@
         <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -852,8 +1006,8 @@
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" t="s">
-        <v>11</v>
+      <c r="F13">
+        <v>0</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -870,13 +1024,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -885,39 +1039,39 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H14" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>418</v>
+        <v>378</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15">
-        <v>0</v>
+      <c r="F15" t="s">
+        <v>11</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -925,8 +1079,8 @@
       <c r="H15" t="s">
         <v>11</v>
       </c>
-      <c r="I15" t="s">
-        <v>11</v>
+      <c r="I15">
+        <v>0</v>
       </c>
       <c r="J15" t="s">
         <v>11</v>
@@ -934,7 +1088,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>456</v>
+        <v>388</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -946,10 +1100,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -957,16 +1111,16 @@
       <c r="H16" t="s">
         <v>11</v>
       </c>
-      <c r="I16" t="s">
-        <v>11</v>
+      <c r="I16">
+        <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>495</v>
+        <v>418</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -975,22 +1129,22 @@
         <v>2</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="H17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" t="s">
+        <v>11</v>
       </c>
       <c r="J17" t="s">
         <v>11</v>
@@ -998,31 +1152,31 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>546</v>
+        <v>456</v>
       </c>
       <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="I18" t="s">
+        <v>11</v>
       </c>
       <c r="J18" t="s">
         <v>11</v>
@@ -1030,13 +1184,13 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>548</v>
+        <v>495</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1045,24 +1199,24 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>-2</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>573</v>
+        <v>546</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1076,25 +1230,25 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" t="s">
-        <v>11</v>
+      <c r="F20">
+        <v>0</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
       </c>
-      <c r="H20">
-        <v>0</v>
+      <c r="H20" t="s">
+        <v>17</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>640</v>
+        <v>548</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -1109,24 +1263,24 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" t="s">
-        <v>11</v>
+        <v>-2</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>661</v>
+        <v>555</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1138,33 +1292,33 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>666</v>
+        <v>573</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1172,31 +1326,31 @@
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23">
-        <v>-2</v>
+      <c r="F23" t="s">
+        <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" t="s">
         <v>10</v>
       </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>710</v>
+        <v>640</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1207,14 +1361,14 @@
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24" t="s">
-        <v>11</v>
+      <c r="G24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
       </c>
       <c r="J24" t="s">
         <v>11</v>
@@ -1222,31 +1376,31 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>740</v>
+        <v>661</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="s">
         <v>11</v>
@@ -1254,25 +1408,25 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>841</v>
+        <v>666</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
-      <c r="C26" t="s">
-        <v>11</v>
+      <c r="C26">
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H26" t="s">
         <v>10</v>
@@ -1286,7 +1440,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>851</v>
+        <v>710</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1301,16 +1455,16 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>-1</v>
-      </c>
-      <c r="G27" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="s">
+        <v>11</v>
       </c>
       <c r="J27" t="s">
         <v>11</v>
@@ -1318,95 +1472,337 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
+        <v>740</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>841</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>851</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>-1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>922</v>
       </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" t="s">
         <v>9</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="6">
+        <f>MIN(B2:B31)</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="6">
+        <f t="shared" ref="C33:I33" si="0">MIN(C2:C31)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E33" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="6">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="G33" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="7"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="8">
+        <f>MAX(B2:B31)</f>
+        <v>1</v>
+      </c>
+      <c r="C34" s="8">
+        <f t="shared" ref="C34:I34" si="1">MAX(C2:C31)</f>
+        <v>2</v>
+      </c>
+      <c r="D34" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E34" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F34" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G34" s="8">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="H34" s="8">
+        <f t="shared" si="1"/>
+        <v>1.75</v>
+      </c>
+      <c r="I34" s="8">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J34" s="9"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B30">
-        <f>AVERAGE(B2:B28)</f>
-        <v>0.57692307692307687</v>
-      </c>
-      <c r="C30">
-        <f>AVERAGE(C2:C28)</f>
-        <v>0.63636363636363635</v>
-      </c>
-      <c r="D30">
-        <f>AVERAGE(D2:D28)</f>
-        <v>0.19230769230769232</v>
-      </c>
-      <c r="E30">
-        <f t="shared" ref="E30:I30" si="0">AVERAGE(E2:E28)</f>
-        <v>0.85185185185185186</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="0"/>
-        <v>-0.58333333333333337</v>
-      </c>
-      <c r="G30">
-        <f>AVERAGE(G2:G28)</f>
+      <c r="B35" s="8">
+        <f>AVERAGE(B2:B31)</f>
+        <v>0.55172413793103448</v>
+      </c>
+      <c r="C35" s="8">
+        <f t="shared" ref="C35:I35" si="2">AVERAGE(C2:C31)</f>
+        <v>0.6</v>
+      </c>
+      <c r="D35" s="8">
+        <f t="shared" si="2"/>
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="E35" s="8">
+        <f t="shared" si="2"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F35" s="8">
+        <f t="shared" si="2"/>
+        <v>-0.55555555555555558</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
-      <c r="H30">
-        <f>AVERAGE(H2:H28)</f>
-        <v>0.21875</v>
-      </c>
-      <c r="I30">
-        <f t="shared" si="0"/>
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="H35" s="8">
+        <f t="shared" si="2"/>
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="I35" s="8">
+        <f t="shared" si="2"/>
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="J35" s="9"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
+      <c r="B36" s="8">
+        <f>MEDIAN(B2:B31)</f>
+        <v>1</v>
+      </c>
+      <c r="C36" s="8">
+        <f t="shared" ref="C36:I36" si="3">MEDIAN(C2:C31)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E36" s="8">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F36" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="8">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="J36" s="9"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" s="10">
+        <f>_xlfn.STDEV.S(B2:B31)</f>
+        <v>0.50612017887847582</v>
+      </c>
+      <c r="C37" s="10">
+        <f t="shared" ref="C37:I37" si="4">_xlfn.STDEV.S(C2:C31)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="D37" s="10">
+        <f t="shared" si="4"/>
+        <v>0.38442587221924479</v>
+      </c>
+      <c r="E37" s="10">
+        <f t="shared" si="4"/>
+        <v>0.37904902178945177</v>
+      </c>
+      <c r="F37" s="10">
+        <f t="shared" si="4"/>
+        <v>0.93369956184785252</v>
+      </c>
+      <c r="G37" s="10">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="H37" s="10">
+        <f t="shared" si="4"/>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="I37" s="10">
+        <f t="shared" si="4"/>
+        <v>0.69724733499228675</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Experience/users_feeling.xlsx
+++ b/Experience/users_feeling.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fortineau_Vin\Documents\GitHub\Thesis_report\Experience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFE81A1-1076-4830-A95F-C3F71CE704E5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71513581-E77A-4436-B4D8-D07E540EC5A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12315" windowHeight="7650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="26">
   <si>
     <t>user</t>
   </si>
@@ -603,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="21.42578125" customWidth="1"/>
@@ -992,13 +992,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>353</v>
+        <v>311</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1007,24 +1007,24 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" t="s">
-        <v>11</v>
+        <v>22</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1042,21 +1042,21 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H14" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1070,31 +1070,31 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15" t="s">
-        <v>11</v>
+      <c r="F15">
+        <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H15" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1102,8 +1102,8 @@
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16">
-        <v>-2</v>
+      <c r="F16" t="s">
+        <v>11</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1115,27 +1115,27 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17">
-        <v>2</v>
+      <c r="C17" t="s">
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1143,28 +1143,28 @@
       <c r="H17" t="s">
         <v>11</v>
       </c>
-      <c r="I17" t="s">
-        <v>11</v>
+      <c r="I17">
+        <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>456</v>
+        <v>418</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" t="s">
-        <v>11</v>
+      <c r="C18">
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1184,31 +1184,31 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>495</v>
+        <v>456</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19">
-        <v>2</v>
+      <c r="C19" t="s">
+        <v>11</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>10</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="H19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" t="s">
+        <v>11</v>
       </c>
       <c r="J19" t="s">
         <v>11</v>
@@ -1216,13 +1216,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>546</v>
+        <v>495</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1231,16 +1231,16 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="s">
         <v>10</v>
       </c>
-      <c r="H20" t="s">
-        <v>17</v>
+      <c r="H20">
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="s">
         <v>11</v>
@@ -1248,13 +1248,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1263,56 +1263,56 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>-2</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>17</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
-        <v>10</v>
+        <v>-2</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1324,10 +1324,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
       </c>
       <c r="G23" t="s">
         <v>10</v>
@@ -1336,21 +1336,21 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>640</v>
+        <v>573</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1358,31 +1358,31 @@
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>0</v>
+      <c r="F24" t="s">
+        <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="s">
         <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="s">
         <v>11</v>
@@ -1408,13 +1408,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G26" t="s">
         <v>9</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="s">
         <v>11</v>
@@ -1440,13 +1440,13 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>710</v>
+        <v>666</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1455,16 +1455,16 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27" t="s">
-        <v>11</v>
+        <v>-2</v>
+      </c>
+      <c r="G27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" t="s">
+        <v>10</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
       </c>
       <c r="J27" t="s">
         <v>11</v>
@@ -1472,31 +1472,31 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>740</v>
+        <v>710</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="G28" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" t="s">
-        <v>11</v>
-      </c>
-      <c r="I28">
-        <v>2</v>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" t="s">
+        <v>11</v>
       </c>
       <c r="J28" t="s">
         <v>11</v>
@@ -1504,31 +1504,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>841</v>
+        <v>740</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
-      <c r="C29" t="s">
-        <v>11</v>
+      <c r="C29">
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="s">
         <v>11</v>
@@ -1536,31 +1536,31 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
         <v>10</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="s">
         <v>11</v>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>922</v>
+        <v>851</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1580,16 +1580,16 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G31" t="s">
         <v>9</v>
       </c>
-      <c r="H31">
-        <v>0</v>
+      <c r="H31" t="s">
+        <v>10</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -1598,199 +1598,228 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>922</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="6">
-        <f>MIN(B2:B31)</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="6">
-        <f t="shared" ref="C33:I33" si="0">MIN(C2:C31)</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="B34" s="6">
+        <f>MIN(B2:B32)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="6">
+        <f t="shared" ref="C34:I34" si="0">MIN(C2:C32)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E34" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F34" s="6">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G34" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H34" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I34" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="7"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
+      <c r="J34" s="7"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="8">
-        <f>MAX(B2:B31)</f>
-        <v>1</v>
-      </c>
-      <c r="C34" s="8">
-        <f t="shared" ref="C34:I34" si="1">MAX(C2:C31)</f>
+      <c r="B35" s="8">
+        <f>MAX(B2:B32)</f>
+        <v>1</v>
+      </c>
+      <c r="C35" s="8">
+        <f t="shared" ref="C35:I35" si="1">MAX(C2:C32)</f>
         <v>2</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D35" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E35" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F35" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G35" s="8">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H35" s="8">
         <f t="shared" si="1"/>
         <v>1.75</v>
       </c>
-      <c r="I34" s="8">
+      <c r="I35" s="8">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J34" s="9"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="J35" s="9"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="8">
-        <f>AVERAGE(B2:B31)</f>
-        <v>0.55172413793103448</v>
-      </c>
-      <c r="C35" s="8">
-        <f t="shared" ref="C35:I35" si="2">AVERAGE(C2:C31)</f>
-        <v>0.6</v>
-      </c>
-      <c r="D35" s="8">
+      <c r="B36" s="8">
+        <f>AVERAGE(B2:B32)</f>
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="C36" s="8">
+        <f t="shared" ref="C36:I36" si="2">AVERAGE(C2:C32)</f>
+        <v>0.65384615384615385</v>
+      </c>
+      <c r="D36" s="8">
         <f t="shared" si="2"/>
-        <v>0.17241379310344829</v>
-      </c>
-      <c r="E35" s="8">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E36" s="8">
         <f t="shared" si="2"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="F35" s="8">
+        <v>0.83870967741935487</v>
+      </c>
+      <c r="F36" s="8">
         <f t="shared" si="2"/>
-        <v>-0.55555555555555558</v>
-      </c>
-      <c r="G35" s="8">
+        <v>-0.6071428571428571</v>
+      </c>
+      <c r="G36" s="8">
         <f t="shared" si="2"/>
         <v>0.125</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H36" s="8">
         <f t="shared" si="2"/>
-        <v>0.19444444444444445</v>
-      </c>
-      <c r="I35" s="8">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="I36" s="8">
         <f t="shared" si="2"/>
-        <v>0.61538461538461542</v>
-      </c>
-      <c r="J35" s="9"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+        <v>0.59259259259259256</v>
+      </c>
+      <c r="J36" s="9"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="8">
-        <f>MEDIAN(B2:B31)</f>
-        <v>1</v>
-      </c>
-      <c r="C36" s="8">
-        <f t="shared" ref="C36:I36" si="3">MEDIAN(C2:C31)</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="8">
+      <c r="B37" s="8">
+        <f>MEDIAN(B2:B32)</f>
+        <v>1</v>
+      </c>
+      <c r="C37" s="8">
+        <f t="shared" ref="C37:I37" si="3">MEDIAN(C2:C32)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D37" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E37" s="8">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F37" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G37" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H37" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I37" s="8">
         <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="J36" s="9"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="J37" s="9"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B37" s="10">
-        <f>_xlfn.STDEV.S(B2:B31)</f>
-        <v>0.50612017887847582</v>
-      </c>
-      <c r="C37" s="10">
-        <f t="shared" ref="C37:I37" si="4">_xlfn.STDEV.S(C2:C31)</f>
-        <v>0.70710678118654757</v>
-      </c>
-      <c r="D37" s="10">
+      <c r="B38" s="10">
+        <f>_xlfn.STDEV.S(B2:B32)</f>
+        <v>0.50400693299373089</v>
+      </c>
+      <c r="C38" s="10">
+        <f t="shared" ref="C38:I38" si="4">_xlfn.STDEV.S(C2:C32)</f>
+        <v>0.74524131352509926</v>
+      </c>
+      <c r="D38" s="10">
         <f t="shared" si="4"/>
-        <v>0.38442587221924479</v>
-      </c>
-      <c r="E37" s="10">
+        <v>0.37904902178945171</v>
+      </c>
+      <c r="E38" s="10">
         <f t="shared" si="4"/>
-        <v>0.37904902178945177</v>
-      </c>
-      <c r="F37" s="10">
+        <v>0.37387825055298307</v>
+      </c>
+      <c r="F38" s="10">
         <f t="shared" si="4"/>
-        <v>0.93369956184785252</v>
-      </c>
-      <c r="G37" s="10">
+        <v>0.95604454081447698</v>
+      </c>
+      <c r="G38" s="10">
         <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H38" s="10">
         <f t="shared" si="4"/>
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="I37" s="10">
+        <v>0.55339859052946638</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="4"/>
-        <v>0.69724733499228675</v>
-      </c>
-      <c r="J37" s="11"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
+        <v>0.69388866648871095</v>
+      </c>
+      <c r="J38" s="11"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
@@ -1803,6 +1832,9 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
